--- a/NJSBCL/data/weekenderscup_schedule.xlsx
+++ b/NJSBCL/data/weekenderscup_schedule.xlsx
@@ -323,7 +323,7 @@
       </c>
       <c t="inlineStr" r="E3">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F3">
@@ -333,22 +333,17 @@
       </c>
       <c t="inlineStr" r="G3">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">Perryville Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="H3">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I3">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J3">
-        <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
     </row>
@@ -368,7 +363,7 @@
       </c>
       <c t="inlineStr" r="E4">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F4">
@@ -378,22 +373,22 @@
       </c>
       <c t="inlineStr" r="G4">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">Pmcc</t>
         </is>
       </c>
       <c t="inlineStr" r="H4">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I4">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J4">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
     </row>
@@ -413,7 +408,7 @@
       </c>
       <c t="inlineStr" r="E5">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F5">
@@ -423,22 +418,22 @@
       </c>
       <c t="inlineStr" r="G5">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">Phoenix Flyers</t>
         </is>
       </c>
       <c t="inlineStr" r="H5">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I5">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J5">
         <is>
-          <t xml:space="preserve">Nj Warriors</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
     </row>
@@ -458,7 +453,7 @@
       </c>
       <c t="inlineStr" r="E6">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F6">
@@ -468,22 +463,22 @@
       </c>
       <c t="inlineStr" r="G6">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">Staten Island Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="H6">
         <is>
-          <t xml:space="preserve">BLOODLINE</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="I6">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="J6">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
     </row>
@@ -503,7 +498,7 @@
       </c>
       <c t="inlineStr" r="E7">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F7">
@@ -513,22 +508,22 @@
       </c>
       <c t="inlineStr" r="G7">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Bethak Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="H7">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
       <c t="inlineStr" r="I7">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
       <c t="inlineStr" r="J7">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
     </row>
@@ -548,7 +543,7 @@
       </c>
       <c t="inlineStr" r="E8">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F8">
@@ -558,22 +553,22 @@
       </c>
       <c t="inlineStr" r="G8">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">Edison Riders</t>
         </is>
       </c>
       <c t="inlineStr" r="H8">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I8">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="J8">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
     </row>
@@ -593,7 +588,7 @@
       </c>
       <c t="inlineStr" r="E9">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F9">
@@ -603,22 +598,22 @@
       </c>
       <c t="inlineStr" r="G9">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H9">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="I9">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="J9">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
     </row>
@@ -638,27 +633,32 @@
       </c>
       <c t="inlineStr" r="E10">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F10">
         <is>
-          <t xml:space="preserve">08:00 AM</t>
+          <t xml:space="preserve">8:00 AM</t>
         </is>
       </c>
       <c t="inlineStr" r="G10">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Robbinsville Jaguars</t>
         </is>
       </c>
       <c t="inlineStr" r="H10">
         <is>
-          <t xml:space="preserve">Jc Mavericks</t>
+          <t xml:space="preserve">TRIDENTS XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I10">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">TBD</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J10">
+        <is>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
       </c>
       <c t="inlineStr" r="E11">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F11">
@@ -688,22 +688,22 @@
       </c>
       <c t="inlineStr" r="G11">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Mag11</t>
         </is>
       </c>
       <c t="inlineStr" r="H11">
         <is>
-          <t xml:space="preserve">CHAMPIONS</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I11">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J11">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c t="inlineStr" r="E12">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F12">
@@ -733,22 +733,22 @@
       </c>
       <c t="inlineStr" r="G12">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">Secaucus Fighters</t>
         </is>
       </c>
       <c t="inlineStr" r="H12">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="I12">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="J12">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c t="inlineStr" r="E13">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F13">
@@ -778,22 +778,22 @@
       </c>
       <c t="inlineStr" r="G13">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">Top Guns</t>
         </is>
       </c>
       <c t="inlineStr" r="H13">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I13">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J13">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c t="inlineStr" r="E14">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F14">
@@ -823,22 +823,22 @@
       </c>
       <c t="inlineStr" r="G14">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">Monroe Giants Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H14">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="I14">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="J14">
         <is>
-          <t xml:space="preserve">TRIDENTS XI</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c t="inlineStr" r="E15">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F15">
@@ -868,22 +868,22 @@
       </c>
       <c t="inlineStr" r="G15">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Sinclair Lions</t>
         </is>
       </c>
       <c t="inlineStr" r="H15">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="I15">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="J15">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c t="inlineStr" r="E16">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F16">
@@ -913,22 +913,22 @@
       </c>
       <c t="inlineStr" r="G16">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">Jersey Aces</t>
         </is>
       </c>
       <c t="inlineStr" r="H16">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I16">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J16">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c t="inlineStr" r="E17">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F17">
@@ -958,22 +958,22 @@
       </c>
       <c t="inlineStr" r="G17">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">EB Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="H17">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I17">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J17">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c t="inlineStr" r="E18">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F18">
@@ -1003,22 +1003,22 @@
       </c>
       <c t="inlineStr" r="G18">
         <is>
-          <t xml:space="preserve">Em Sports Club</t>
+          <t xml:space="preserve">Firehawks</t>
         </is>
       </c>
       <c t="inlineStr" r="H18">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I18">
         <is>
-          <t xml:space="preserve">EM Sports Club</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J18">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c t="inlineStr" r="E19">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F19">
@@ -1048,22 +1048,17 @@
       </c>
       <c t="inlineStr" r="G19">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">NJ Marvels</t>
         </is>
       </c>
       <c t="inlineStr" r="H19">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">Nj Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I19">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J19">
-        <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">NJ Warriors</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1078,7 @@
       </c>
       <c t="inlineStr" r="E20">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F20">
@@ -1093,22 +1088,22 @@
       </c>
       <c t="inlineStr" r="G20">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Giant Slayers</t>
         </is>
       </c>
       <c t="inlineStr" r="H20">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="I20">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="J20">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1123,7 @@
       </c>
       <c t="inlineStr" r="E21">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F21">
@@ -1138,22 +1133,22 @@
       </c>
       <c t="inlineStr" r="G21">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">Pway Cubs</t>
         </is>
       </c>
       <c t="inlineStr" r="H21">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="I21">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="J21">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1168,7 @@
       </c>
       <c t="inlineStr" r="E22">
         <is>
-          <t xml:space="preserve">08/29/2026</t>
+          <t xml:space="preserve">09/20/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F22">
@@ -1183,22 +1178,22 @@
       </c>
       <c t="inlineStr" r="G22">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">United Falcons</t>
         </is>
       </c>
       <c t="inlineStr" r="H22">
         <is>
-          <t xml:space="preserve">JERSEY TIGERS</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I22">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J22">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1213,7 @@
       </c>
       <c t="inlineStr" r="E23">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F23">
@@ -1228,22 +1223,22 @@
       </c>
       <c t="inlineStr" r="G23">
         <is>
-          <t xml:space="preserve">Perryville Panthers</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
       <c t="inlineStr" r="H23">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I23">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
       <c t="inlineStr" r="J23">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1258,7 @@
       </c>
       <c t="inlineStr" r="E24">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F24">
@@ -1273,22 +1268,22 @@
       </c>
       <c t="inlineStr" r="G24">
         <is>
-          <t xml:space="preserve">Pmcc</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H24">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
       <c t="inlineStr" r="I24">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J24">
         <is>
-          <t xml:space="preserve">Em Sports Club</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1303,7 @@
       </c>
       <c t="inlineStr" r="E25">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F25">
@@ -1318,22 +1313,22 @@
       </c>
       <c t="inlineStr" r="G25">
         <is>
-          <t xml:space="preserve">Phoenix Flyers</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="H25">
         <is>
+          <t xml:space="preserve">Mystery Squad</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I25">
+        <is>
+          <t xml:space="preserve">Troy Titans</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J25">
+        <is>
           <t xml:space="preserve">MCC - Weekenders</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I25">
-        <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J25">
-        <is>
-          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1348,7 @@
       </c>
       <c t="inlineStr" r="E26">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F26">
@@ -1363,22 +1358,22 @@
       </c>
       <c t="inlineStr" r="G26">
         <is>
-          <t xml:space="preserve">Staten Island Strikers</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H26">
         <is>
+          <t xml:space="preserve">JERSEY TIGERS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I26">
+        <is>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J26">
+        <is>
           <t xml:space="preserve">Sparta XI</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I26">
-        <is>
-          <t xml:space="preserve">Sparta XI</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J26">
-        <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1393,7 @@
       </c>
       <c t="inlineStr" r="E27">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F27">
@@ -1408,22 +1403,22 @@
       </c>
       <c t="inlineStr" r="G27">
         <is>
-          <t xml:space="preserve">Bethak Titans</t>
+          <t xml:space="preserve">Em Sports Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H27">
         <is>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I27">
+        <is>
+          <t xml:space="preserve">EM Sports Club</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J27">
+        <is>
           <t xml:space="preserve">Bayonne CC</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I27">
-        <is>
-          <t xml:space="preserve">Bayonne CC</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J27">
-        <is>
-          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1438,7 @@
       </c>
       <c t="inlineStr" r="E28">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F28">
@@ -1453,22 +1448,22 @@
       </c>
       <c t="inlineStr" r="G28">
         <is>
-          <t xml:space="preserve">Edison Riders</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="H28">
         <is>
+          <t xml:space="preserve">Kranti Warriors</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I28">
+        <is>
+          <t xml:space="preserve">JC Warriors</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J28">
+        <is>
           <t xml:space="preserve">Jersey Sloggers</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I28">
-        <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J28">
-        <is>
-          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1483,7 @@
       </c>
       <c t="inlineStr" r="E29">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F29">
@@ -1498,22 +1493,22 @@
       </c>
       <c t="inlineStr" r="G29">
         <is>
-          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="H29">
         <is>
+          <t xml:space="preserve">Invincible CC</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I29">
+        <is>
+          <t xml:space="preserve">Monroe Mavericks</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J29">
+        <is>
           <t xml:space="preserve">Newport Narcos</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I29">
-        <is>
-          <t xml:space="preserve">Newport Narcos</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J29">
-        <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1528,7 @@
       </c>
       <c t="inlineStr" r="E30">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F30">
@@ -1543,22 +1538,22 @@
       </c>
       <c t="inlineStr" r="G30">
         <is>
-          <t xml:space="preserve">Robbinsville Jaguars</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
       <c t="inlineStr" r="H30">
         <is>
+          <t xml:space="preserve">Monroe United</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I30">
+        <is>
+          <t xml:space="preserve">Express Rangers</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J30">
+        <is>
           <t xml:space="preserve">Parsippany Super Kings</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I30">
-        <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J30">
-        <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
     </row>
@@ -1578,32 +1573,32 @@
       </c>
       <c t="inlineStr" r="E31">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F31">
         <is>
-          <t xml:space="preserve">8:00 AM</t>
+          <t xml:space="preserve">08:00 AM</t>
         </is>
       </c>
       <c t="inlineStr" r="G31">
         <is>
-          <t xml:space="preserve">Mag11</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
       <c t="inlineStr" r="H31">
         <is>
+          <t xml:space="preserve">Iselin Warriors</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I31">
+        <is>
+          <t xml:space="preserve">Princeton Walk</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J31">
+        <is>
           <t xml:space="preserve">PCA Jr.</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I31">
-        <is>
-          <t xml:space="preserve">TBD</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J31">
-        <is>
-          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1618,7 @@
       </c>
       <c t="inlineStr" r="E32">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F32">
@@ -1633,22 +1628,22 @@
       </c>
       <c t="inlineStr" r="G32">
         <is>
-          <t xml:space="preserve">Secaucus Fighters</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
       <c t="inlineStr" r="H32">
         <is>
+          <t xml:space="preserve">NJKnights</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I32">
+        <is>
+          <t xml:space="preserve">Plainsboro Hunters</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J32">
+        <is>
           <t xml:space="preserve">TRIDENTS XI</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I32">
-        <is>
-          <t xml:space="preserve">Tridents XI</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J32">
-        <is>
-          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1663,7 @@
       </c>
       <c t="inlineStr" r="E33">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F33">
@@ -1678,22 +1673,22 @@
       </c>
       <c t="inlineStr" r="G33">
         <is>
-          <t xml:space="preserve">Top Guns</t>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H33">
         <is>
+          <t xml:space="preserve">Power Hitters</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I33">
+        <is>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J33">
+        <is>
           <t xml:space="preserve">Jersey Superstars</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I33">
-        <is>
-          <t xml:space="preserve">Jersey Superstars</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J33">
-        <is>
-          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1708,7 @@
       </c>
       <c t="inlineStr" r="E34">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F34">
@@ -1723,22 +1718,22 @@
       </c>
       <c t="inlineStr" r="G34">
         <is>
-          <t xml:space="preserve">Monroe Giants Club</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
       <c t="inlineStr" r="H34">
         <is>
+          <t xml:space="preserve">Woodlot Boyz</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I34">
+        <is>
+          <t xml:space="preserve">NJ Boxers</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J34">
+        <is>
           <t xml:space="preserve">Windsor Warriors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I34">
-        <is>
-          <t xml:space="preserve">Windsor Warriors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J34">
-        <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1753,7 @@
       </c>
       <c t="inlineStr" r="E35">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F35">
@@ -1768,22 +1763,22 @@
       </c>
       <c t="inlineStr" r="G35">
         <is>
-          <t xml:space="preserve">Sinclair Lions</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
       <c t="inlineStr" r="H35">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I35">
         <is>
+          <t xml:space="preserve">VRK Gladiators</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J35">
+        <is>
           <t xml:space="preserve">Lincoln XI</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J35">
-        <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1798,7 @@
       </c>
       <c t="inlineStr" r="E36">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F36">
@@ -1813,22 +1808,22 @@
       </c>
       <c t="inlineStr" r="G36">
         <is>
-          <t xml:space="preserve">Jersey Aces</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="H36">
         <is>
+          <t xml:space="preserve">CHAMPIONS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I36">
+        <is>
+          <t xml:space="preserve">Edison Warriors</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J36">
+        <is>
           <t xml:space="preserve">Raptors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I36">
-        <is>
-          <t xml:space="preserve">Raptors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J36">
-        <is>
-          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1843,7 @@
       </c>
       <c t="inlineStr" r="E37">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F37">
@@ -1858,22 +1853,22 @@
       </c>
       <c t="inlineStr" r="G37">
         <is>
-          <t xml:space="preserve">EB Strikers</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H37">
         <is>
+          <t xml:space="preserve">Jc Mavericks</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I37">
+        <is>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J37">
+        <is>
           <t xml:space="preserve">Brown Munde</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I37">
-        <is>
-          <t xml:space="preserve">Brown Munde</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J37">
-        <is>
-          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1888,7 @@
       </c>
       <c t="inlineStr" r="E38">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F38">
@@ -1903,22 +1898,22 @@
       </c>
       <c t="inlineStr" r="G38">
         <is>
-          <t xml:space="preserve">Firehawks</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
       <c t="inlineStr" r="H38">
         <is>
+          <t xml:space="preserve">Morris Indians</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I38">
+        <is>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J38">
+        <is>
           <t xml:space="preserve">Trident CC</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I38">
-        <is>
-          <t xml:space="preserve">Trident CC</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J38">
-        <is>
-          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1933,7 @@
       </c>
       <c t="inlineStr" r="E39">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F39">
@@ -1948,22 +1943,22 @@
       </c>
       <c t="inlineStr" r="G39">
         <is>
-          <t xml:space="preserve">NJ Marvels</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
       <c t="inlineStr" r="H39">
         <is>
+          <t xml:space="preserve">Jersey City Dominators</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I39">
+        <is>
+          <t xml:space="preserve">Karma XI</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J39">
+        <is>
           <t xml:space="preserve">Waterfront Warriors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I39">
-        <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J39">
-        <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1978,7 @@
       </c>
       <c t="inlineStr" r="E40">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F40">
@@ -1993,22 +1988,22 @@
       </c>
       <c t="inlineStr" r="G40">
         <is>
-          <t xml:space="preserve">Giant Slayers</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
       <c t="inlineStr" r="H40">
         <is>
+          <t xml:space="preserve">NJ Titans</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I40">
+        <is>
+          <t xml:space="preserve">Cricket Lovers</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J40">
+        <is>
           <t xml:space="preserve">Thunder Strikers Weekenders</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I40">
-        <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J40">
-        <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2023,7 @@
       </c>
       <c t="inlineStr" r="E41">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F41">
@@ -2038,22 +2033,22 @@
       </c>
       <c t="inlineStr" r="G41">
         <is>
-          <t xml:space="preserve">Pway Cubs</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="H41">
         <is>
+          <t xml:space="preserve">BLOODLINE</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I41">
+        <is>
+          <t xml:space="preserve">Edison Super Kings</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J41">
+        <is>
           <t xml:space="preserve">Nj Warriors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I41">
-        <is>
-          <t xml:space="preserve">NJ Warriors</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J41">
-        <is>
-          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2068,7 @@
       </c>
       <c t="inlineStr" r="E42">
         <is>
-          <t xml:space="preserve">08/30/2026</t>
+          <t xml:space="preserve">09/19/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F42">
@@ -2083,22 +2078,22 @@
       </c>
       <c t="inlineStr" r="G42">
         <is>
-          <t xml:space="preserve">United Falcons</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H42">
         <is>
+          <t xml:space="preserve">Vikings CC</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I42">
+        <is>
+          <t xml:space="preserve">RCW - Weekenders</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J42">
+        <is>
           <t xml:space="preserve">Incredibulls</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I42">
-        <is>
-          <t xml:space="preserve">Incredibulls</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J42">
-        <is>
-          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2113,7 @@
       </c>
       <c t="inlineStr" r="E43">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F43">
@@ -2128,22 +2123,22 @@
       </c>
       <c t="inlineStr" r="G43">
         <is>
-          <t xml:space="preserve">Perryville Panthers</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
       <c t="inlineStr" r="H43">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
       <c t="inlineStr" r="I43">
         <is>
-          <t xml:space="preserve">Perryville Panthers</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
       <c t="inlineStr" r="J43">
         <is>
-          <t xml:space="preserve">JERSEY TIGERS</t>
+          <t xml:space="preserve">Robbinsville Jaguars</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2158,7 @@
       </c>
       <c t="inlineStr" r="E44">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F44">
@@ -2173,22 +2168,22 @@
       </c>
       <c t="inlineStr" r="G44">
         <is>
-          <t xml:space="preserve">Pmcc</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H44">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I44">
         <is>
-          <t xml:space="preserve">PMCC</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="J44">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2203,7 @@
       </c>
       <c t="inlineStr" r="E45">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F45">
@@ -2218,22 +2213,22 @@
       </c>
       <c t="inlineStr" r="G45">
         <is>
-          <t xml:space="preserve">Phoenix Flyers</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="H45">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">JERSEY TIGERS</t>
         </is>
       </c>
       <c t="inlineStr" r="I45">
         <is>
-          <t xml:space="preserve">Phoenix Flyers</t>
+          <t xml:space="preserve">Jersey Tigers</t>
         </is>
       </c>
       <c t="inlineStr" r="J45">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">Mag11</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2248,7 @@
       </c>
       <c t="inlineStr" r="E46">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F46">
@@ -2263,22 +2258,22 @@
       </c>
       <c t="inlineStr" r="G46">
         <is>
-          <t xml:space="preserve">Staten Island Strikers</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H46">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I46">
         <is>
-          <t xml:space="preserve">Staten Island Strikers</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J46">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">Secaucus Fighters</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2293,7 @@
       </c>
       <c t="inlineStr" r="E47">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F47">
@@ -2308,22 +2303,22 @@
       </c>
       <c t="inlineStr" r="G47">
         <is>
-          <t xml:space="preserve">Bethak Titans</t>
+          <t xml:space="preserve">Em Sports Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H47">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I47">
         <is>
-          <t xml:space="preserve">Bethak Titans</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J47">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Perryville Panthers</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2338,7 @@
       </c>
       <c t="inlineStr" r="E48">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F48">
@@ -2353,22 +2348,22 @@
       </c>
       <c t="inlineStr" r="G48">
         <is>
-          <t xml:space="preserve">Edison Riders</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="H48">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I48">
         <is>
-          <t xml:space="preserve">Edison Riders</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J48">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">Pmcc</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2383,7 @@
       </c>
       <c t="inlineStr" r="E49">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F49">
@@ -2398,22 +2393,22 @@
       </c>
       <c t="inlineStr" r="G49">
         <is>
-          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="H49">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">Monroe United</t>
         </is>
       </c>
       <c t="inlineStr" r="I49">
         <is>
-          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
+          <t xml:space="preserve">Monroe United</t>
         </is>
       </c>
       <c t="inlineStr" r="J49">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">Phoenix Flyers</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2428,7 @@
       </c>
       <c t="inlineStr" r="E50">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F50">
@@ -2443,22 +2438,22 @@
       </c>
       <c t="inlineStr" r="G50">
         <is>
-          <t xml:space="preserve">Robbinsville Jaguars</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
       <c t="inlineStr" r="H50">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I50">
         <is>
-          <t xml:space="preserve">Robbinsville Jaguars</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J50">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">Staten Island Strikers</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2473,7 @@
       </c>
       <c t="inlineStr" r="E51">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F51">
@@ -2488,22 +2483,22 @@
       </c>
       <c t="inlineStr" r="G51">
         <is>
-          <t xml:space="preserve">Mag11</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
       <c t="inlineStr" r="H51">
         <is>
-          <t xml:space="preserve">TRIDENTS XI</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
       <c t="inlineStr" r="I51">
         <is>
-          <t xml:space="preserve">Mag11</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
       <c t="inlineStr" r="J51">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">Bethak Titans</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2518,7 @@
       </c>
       <c t="inlineStr" r="E52">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F52">
@@ -2533,22 +2528,22 @@
       </c>
       <c t="inlineStr" r="G52">
         <is>
-          <t xml:space="preserve">Secaucus Fighters</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
       <c t="inlineStr" r="H52">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
       <c t="inlineStr" r="I52">
         <is>
-          <t xml:space="preserve">Secaucus Fighters</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
       <c t="inlineStr" r="J52">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">Edison Riders</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2563,7 @@
       </c>
       <c t="inlineStr" r="E53">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F53">
@@ -2578,22 +2573,22 @@
       </c>
       <c t="inlineStr" r="G53">
         <is>
-          <t xml:space="preserve">Top Guns</t>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H53">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
       <c t="inlineStr" r="I53">
         <is>
-          <t xml:space="preserve">Top Guns</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
       <c t="inlineStr" r="J53">
         <is>
-          <t xml:space="preserve">CHAMPIONS</t>
+          <t xml:space="preserve">NJ Marvels</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2608,7 @@
       </c>
       <c t="inlineStr" r="E54">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F54">
@@ -2623,22 +2618,22 @@
       </c>
       <c t="inlineStr" r="G54">
         <is>
-          <t xml:space="preserve">Monroe Giants Club</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
       <c t="inlineStr" r="H54">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I54">
         <is>
-          <t xml:space="preserve">Monroe Giants Club</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J54">
         <is>
-          <t xml:space="preserve">Jc Mavericks</t>
+          <t xml:space="preserve">Giant Slayers</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2653,7 @@
       </c>
       <c t="inlineStr" r="E55">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F55">
@@ -2668,22 +2663,22 @@
       </c>
       <c t="inlineStr" r="G55">
         <is>
-          <t xml:space="preserve">Sinclair Lions</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
       <c t="inlineStr" r="H55">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">CHAMPIONS</t>
         </is>
       </c>
       <c t="inlineStr" r="I55">
         <is>
-          <t xml:space="preserve">Sinclair Lions</t>
+          <t xml:space="preserve">Champions</t>
         </is>
       </c>
       <c t="inlineStr" r="J55">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">Pway Cubs</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2698,7 @@
       </c>
       <c t="inlineStr" r="E56">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F56">
@@ -2713,22 +2708,22 @@
       </c>
       <c t="inlineStr" r="G56">
         <is>
-          <t xml:space="preserve">Jersey Aces</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="H56">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">Jc Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="I56">
         <is>
-          <t xml:space="preserve">Jersey Aces</t>
+          <t xml:space="preserve">JC Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="J56">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">United Falcons</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2743,7 @@
       </c>
       <c t="inlineStr" r="E57">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F57">
@@ -2758,22 +2753,22 @@
       </c>
       <c t="inlineStr" r="G57">
         <is>
-          <t xml:space="preserve">EB Strikers</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H57">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
       <c t="inlineStr" r="I57">
         <is>
-          <t xml:space="preserve">EB Strikers</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
       <c t="inlineStr" r="J57">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Top Guns</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2788,7 @@
       </c>
       <c t="inlineStr" r="E58">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F58">
@@ -2803,22 +2798,22 @@
       </c>
       <c t="inlineStr" r="G58">
         <is>
-          <t xml:space="preserve">Firehawks</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
       <c t="inlineStr" r="H58">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
       <c t="inlineStr" r="I58">
         <is>
-          <t xml:space="preserve">Firehawks</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
       <c t="inlineStr" r="J58">
         <is>
-          <t xml:space="preserve">BLOODLINE</t>
+          <t xml:space="preserve">Monroe Giants Club</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2833,7 @@
       </c>
       <c t="inlineStr" r="E59">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F59">
@@ -2848,22 +2843,22 @@
       </c>
       <c t="inlineStr" r="G59">
         <is>
-          <t xml:space="preserve">NJ Marvels</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
       <c t="inlineStr" r="H59">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="I59">
         <is>
-          <t xml:space="preserve">NJ Marvels</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="J59">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">Sinclair Lions</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2878,7 @@
       </c>
       <c t="inlineStr" r="E60">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F60">
@@ -2893,22 +2888,17 @@
       </c>
       <c t="inlineStr" r="G60">
         <is>
-          <t xml:space="preserve">Giant Slayers</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
       <c t="inlineStr" r="H60">
         <is>
-          <t xml:space="preserve">Nj Warriors</t>
+          <t xml:space="preserve">BLOODLINE</t>
         </is>
       </c>
       <c t="inlineStr" r="I60">
         <is>
-          <t xml:space="preserve">Giant Slayers</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J60">
-        <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">Bloodline</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2918,7 @@
       </c>
       <c t="inlineStr" r="E61">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F61">
@@ -2938,22 +2928,22 @@
       </c>
       <c t="inlineStr" r="G61">
         <is>
-          <t xml:space="preserve">Pway Cubs</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="H61">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I61">
         <is>
-          <t xml:space="preserve">Pway Cubs</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J61">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">EB Strikers</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2963,7 @@
       </c>
       <c t="inlineStr" r="E62">
         <is>
-          <t xml:space="preserve">09/12/2026</t>
+          <t xml:space="preserve">09/13/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F62">
@@ -2983,22 +2973,22 @@
       </c>
       <c t="inlineStr" r="G62">
         <is>
-          <t xml:space="preserve">United Falcons</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H62">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
       <c t="inlineStr" r="I62">
         <is>
-          <t xml:space="preserve">United Falcons</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
       <c t="inlineStr" r="J62">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">Firehawks</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3008,7 @@
       </c>
       <c t="inlineStr" r="E63">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F63">
@@ -3028,22 +3018,22 @@
       </c>
       <c t="inlineStr" r="G63">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">United Falcons</t>
         </is>
       </c>
       <c t="inlineStr" r="H63">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="I63">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">United Falcons</t>
         </is>
       </c>
       <c t="inlineStr" r="J63">
         <is>
-          <t xml:space="preserve">Firehawks</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3053,7 @@
       </c>
       <c t="inlineStr" r="E64">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F64">
@@ -3073,22 +3063,22 @@
       </c>
       <c t="inlineStr" r="G64">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">Pway Cubs</t>
         </is>
       </c>
       <c t="inlineStr" r="H64">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="I64">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">Pway Cubs</t>
         </is>
       </c>
       <c t="inlineStr" r="J64">
         <is>
-          <t xml:space="preserve">EB Strikers</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3098,7 @@
       </c>
       <c t="inlineStr" r="E65">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F65">
@@ -3118,22 +3108,22 @@
       </c>
       <c t="inlineStr" r="G65">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">Giant Slayers</t>
         </is>
       </c>
       <c t="inlineStr" r="H65">
         <is>
-          <t xml:space="preserve">BLOODLINE</t>
+          <t xml:space="preserve">Nj Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I65">
         <is>
-          <t xml:space="preserve">Bloodline</t>
+          <t xml:space="preserve">Giant Slayers</t>
         </is>
       </c>
       <c t="inlineStr" r="J65">
         <is>
-          <t xml:space="preserve">Jersey Aces</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
     </row>
@@ -3153,7 +3143,7 @@
       </c>
       <c t="inlineStr" r="E66">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F66">
@@ -3163,22 +3153,22 @@
       </c>
       <c t="inlineStr" r="G66">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">NJ Marvels</t>
         </is>
       </c>
       <c t="inlineStr" r="H66">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I66">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">NJ Marvels</t>
         </is>
       </c>
       <c t="inlineStr" r="J66">
         <is>
-          <t xml:space="preserve">Sinclair Lions</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3188,7 @@
       </c>
       <c t="inlineStr" r="E67">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F67">
@@ -3208,22 +3198,22 @@
       </c>
       <c t="inlineStr" r="G67">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Firehawks</t>
         </is>
       </c>
       <c t="inlineStr" r="H67">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I67">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Firehawks</t>
         </is>
       </c>
       <c t="inlineStr" r="J67">
         <is>
-          <t xml:space="preserve">Monroe Giants Club</t>
+          <t xml:space="preserve">BLOODLINE</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3233,7 @@
       </c>
       <c t="inlineStr" r="E68">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F68">
@@ -3253,22 +3243,22 @@
       </c>
       <c t="inlineStr" r="G68">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">EB Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="H68">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I68">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">EB Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="J68">
         <is>
-          <t xml:space="preserve">Top Guns</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3278,7 @@
       </c>
       <c t="inlineStr" r="E69">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F69">
@@ -3298,22 +3288,22 @@
       </c>
       <c t="inlineStr" r="G69">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">Jersey Aces</t>
         </is>
       </c>
       <c t="inlineStr" r="H69">
         <is>
-          <t xml:space="preserve">Jc Mavericks</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="I69">
         <is>
-          <t xml:space="preserve">JC Mavericks</t>
+          <t xml:space="preserve">Jersey Aces</t>
         </is>
       </c>
       <c t="inlineStr" r="J69">
         <is>
-          <t xml:space="preserve">United Falcons</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3323,7 @@
       </c>
       <c t="inlineStr" r="E70">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F70">
@@ -3343,22 +3333,22 @@
       </c>
       <c t="inlineStr" r="G70">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Sinclair Lions</t>
         </is>
       </c>
       <c t="inlineStr" r="H70">
         <is>
-          <t xml:space="preserve">CHAMPIONS</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="I70">
         <is>
-          <t xml:space="preserve">Champions</t>
+          <t xml:space="preserve">Sinclair Lions</t>
         </is>
       </c>
       <c t="inlineStr" r="J70">
         <is>
-          <t xml:space="preserve">Pway Cubs</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3368,7 @@
       </c>
       <c t="inlineStr" r="E71">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F71">
@@ -3388,22 +3378,22 @@
       </c>
       <c t="inlineStr" r="G71">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Monroe Giants Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H71">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I71">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">Monroe Giants Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J71">
         <is>
-          <t xml:space="preserve">Giant Slayers</t>
+          <t xml:space="preserve">Jc Mavericks</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3413,7 @@
       </c>
       <c t="inlineStr" r="E72">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F72">
@@ -3433,22 +3423,22 @@
       </c>
       <c t="inlineStr" r="G72">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">Top Guns</t>
         </is>
       </c>
       <c t="inlineStr" r="H72">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I72">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">Top Guns</t>
         </is>
       </c>
       <c t="inlineStr" r="J72">
         <is>
-          <t xml:space="preserve">NJ Marvels</t>
+          <t xml:space="preserve">CHAMPIONS</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3458,7 @@
       </c>
       <c t="inlineStr" r="E73">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F73">
@@ -3478,22 +3468,22 @@
       </c>
       <c t="inlineStr" r="G73">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">Secaucus Fighters</t>
         </is>
       </c>
       <c t="inlineStr" r="H73">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I73">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">Secaucus Fighters</t>
         </is>
       </c>
       <c t="inlineStr" r="J73">
         <is>
-          <t xml:space="preserve">Edison Riders</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3503,7 @@
       </c>
       <c t="inlineStr" r="E74">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F74">
@@ -3523,22 +3513,22 @@
       </c>
       <c t="inlineStr" r="G74">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">Mag11</t>
         </is>
       </c>
       <c t="inlineStr" r="H74">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">TRIDENTS XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I74">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">Mag11</t>
         </is>
       </c>
       <c t="inlineStr" r="J74">
         <is>
-          <t xml:space="preserve">Bethak Titans</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3548,7 @@
       </c>
       <c t="inlineStr" r="E75">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F75">
@@ -3568,22 +3558,22 @@
       </c>
       <c t="inlineStr" r="G75">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Robbinsville Jaguars</t>
         </is>
       </c>
       <c t="inlineStr" r="H75">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="I75">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">Robbinsville Jaguars</t>
         </is>
       </c>
       <c t="inlineStr" r="J75">
         <is>
-          <t xml:space="preserve">Staten Island Strikers</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3593,7 @@
       </c>
       <c t="inlineStr" r="E76">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F76">
@@ -3613,22 +3603,22 @@
       </c>
       <c t="inlineStr" r="G76">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H76">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I76">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J76">
         <is>
-          <t xml:space="preserve">Phoenix Flyers</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3638,7 @@
       </c>
       <c t="inlineStr" r="E77">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F77">
@@ -3658,22 +3648,22 @@
       </c>
       <c t="inlineStr" r="G77">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">Edison Riders</t>
         </is>
       </c>
       <c t="inlineStr" r="H77">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
       <c t="inlineStr" r="I77">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">Edison Riders</t>
         </is>
       </c>
       <c t="inlineStr" r="J77">
         <is>
-          <t xml:space="preserve">Pmcc</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3683,7 @@
       </c>
       <c t="inlineStr" r="E78">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F78">
@@ -3703,22 +3693,22 @@
       </c>
       <c t="inlineStr" r="G78">
         <is>
-          <t xml:space="preserve">Em Sports Club</t>
+          <t xml:space="preserve">Bethak Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="H78">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="I78">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">Bethak Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="J78">
         <is>
-          <t xml:space="preserve">Perryville Panthers</t>
+          <t xml:space="preserve">Monroe United</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3728,7 @@
       </c>
       <c t="inlineStr" r="E79">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F79">
@@ -3748,22 +3738,22 @@
       </c>
       <c t="inlineStr" r="G79">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">Staten Island Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="H79">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I79">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">Staten Island Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="J79">
         <is>
-          <t xml:space="preserve">Secaucus Fighters</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
     </row>
@@ -3783,7 +3773,7 @@
       </c>
       <c t="inlineStr" r="E80">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F80">
@@ -3793,22 +3783,22 @@
       </c>
       <c t="inlineStr" r="G80">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Phoenix Flyers</t>
         </is>
       </c>
       <c t="inlineStr" r="H80">
         <is>
-          <t xml:space="preserve">JERSEY TIGERS</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I80">
         <is>
-          <t xml:space="preserve">Jersey Tigers</t>
+          <t xml:space="preserve">Phoenix Flyers</t>
         </is>
       </c>
       <c t="inlineStr" r="J80">
         <is>
-          <t xml:space="preserve">Mag11</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3818,7 @@
       </c>
       <c t="inlineStr" r="E81">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F81">
@@ -3838,22 +3828,22 @@
       </c>
       <c t="inlineStr" r="G81">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">Pmcc</t>
         </is>
       </c>
       <c t="inlineStr" r="H81">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I81">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">PMCC</t>
         </is>
       </c>
       <c t="inlineStr" r="J81">
         <is>
-          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3863,7 @@
       </c>
       <c t="inlineStr" r="E82">
         <is>
-          <t xml:space="preserve">09/13/2026</t>
+          <t xml:space="preserve">09/12/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F82">
@@ -3883,22 +3873,22 @@
       </c>
       <c t="inlineStr" r="G82">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">Perryville Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="H82">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="I82">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">Perryville Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="J82">
         <is>
-          <t xml:space="preserve">Robbinsville Jaguars</t>
+          <t xml:space="preserve">JERSEY TIGERS</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3908,7 @@
       </c>
       <c t="inlineStr" r="E83">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F83">
@@ -3928,22 +3918,22 @@
       </c>
       <c t="inlineStr" r="G83">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">United Falcons</t>
         </is>
       </c>
       <c t="inlineStr" r="H83">
         <is>
-          <t xml:space="preserve">Vikings CC</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="I83">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
       <c t="inlineStr" r="J83">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3953,7 @@
       </c>
       <c t="inlineStr" r="E84">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F84">
@@ -3973,22 +3963,22 @@
       </c>
       <c t="inlineStr" r="G84">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">Pway Cubs</t>
         </is>
       </c>
       <c t="inlineStr" r="H84">
         <is>
-          <t xml:space="preserve">BLOODLINE</t>
+          <t xml:space="preserve">Nj Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I84">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">NJ Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J84">
         <is>
-          <t xml:space="preserve">Nj Warriors</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
     </row>
@@ -4008,7 +3998,7 @@
       </c>
       <c t="inlineStr" r="E85">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F85">
@@ -4018,22 +4008,22 @@
       </c>
       <c t="inlineStr" r="G85">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">Giant Slayers</t>
         </is>
       </c>
       <c t="inlineStr" r="H85">
         <is>
-          <t xml:space="preserve">NJ Titans</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I85">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J85">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
     </row>
@@ -4053,7 +4043,7 @@
       </c>
       <c t="inlineStr" r="E86">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F86">
@@ -4063,22 +4053,22 @@
       </c>
       <c t="inlineStr" r="G86">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">NJ Marvels</t>
         </is>
       </c>
       <c t="inlineStr" r="H86">
         <is>
-          <t xml:space="preserve">Jersey City Dominators</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I86">
         <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J86">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4088,7 @@
       </c>
       <c t="inlineStr" r="E87">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F87">
@@ -4108,22 +4098,22 @@
       </c>
       <c t="inlineStr" r="G87">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Firehawks</t>
         </is>
       </c>
       <c t="inlineStr" r="H87">
         <is>
-          <t xml:space="preserve">Morris Indians</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I87">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J87">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4133,7 @@
       </c>
       <c t="inlineStr" r="E88">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F88">
@@ -4153,22 +4143,22 @@
       </c>
       <c t="inlineStr" r="G88">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">EB Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="H88">
         <is>
-          <t xml:space="preserve">Jc Mavericks</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="I88">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
       <c t="inlineStr" r="J88">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4178,7 @@
       </c>
       <c t="inlineStr" r="E89">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F89">
@@ -4198,22 +4188,22 @@
       </c>
       <c t="inlineStr" r="G89">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">Jersey Aces</t>
         </is>
       </c>
       <c t="inlineStr" r="H89">
         <is>
-          <t xml:space="preserve">CHAMPIONS</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="I89">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">Raptors</t>
         </is>
       </c>
       <c t="inlineStr" r="J89">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4223,7 @@
       </c>
       <c t="inlineStr" r="E90">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F90">
@@ -4243,22 +4233,22 @@
       </c>
       <c t="inlineStr" r="G90">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Sinclair Lions</t>
         </is>
       </c>
       <c t="inlineStr" r="H90">
         <is>
-          <t xml:space="preserve">Shreeji XI</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I90">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J90">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4268,7 @@
       </c>
       <c t="inlineStr" r="E91">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F91">
@@ -4288,22 +4278,22 @@
       </c>
       <c t="inlineStr" r="G91">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Monroe Giants Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H91">
         <is>
-          <t xml:space="preserve">Woodlot Boyz</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I91">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J91">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4313,7 @@
       </c>
       <c t="inlineStr" r="E92">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F92">
@@ -4333,22 +4323,22 @@
       </c>
       <c t="inlineStr" r="G92">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">Top Guns</t>
         </is>
       </c>
       <c t="inlineStr" r="H92">
         <is>
-          <t xml:space="preserve">Power Hitters</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="I92">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
       <c t="inlineStr" r="J92">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4358,7 @@
       </c>
       <c t="inlineStr" r="E93">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F93">
@@ -4378,22 +4368,22 @@
       </c>
       <c t="inlineStr" r="G93">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">Secaucus Fighters</t>
         </is>
       </c>
       <c t="inlineStr" r="H93">
         <is>
-          <t xml:space="preserve">NJKnights</t>
+          <t xml:space="preserve">TRIDENTS XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I93">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">Tridents XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J93">
         <is>
-          <t xml:space="preserve">TRIDENTS XI</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
     </row>
@@ -4413,32 +4403,32 @@
       </c>
       <c t="inlineStr" r="E94">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F94">
         <is>
-          <t xml:space="preserve">08:00 AM</t>
+          <t xml:space="preserve">8:00 AM</t>
         </is>
       </c>
       <c t="inlineStr" r="G94">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">Mag11</t>
         </is>
       </c>
       <c t="inlineStr" r="H94">
         <is>
-          <t xml:space="preserve">Iselin Warriors</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
       <c t="inlineStr" r="I94">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">TBD</t>
         </is>
       </c>
       <c t="inlineStr" r="J94">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4448,7 @@
       </c>
       <c t="inlineStr" r="E95">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F95">
@@ -4468,22 +4458,22 @@
       </c>
       <c t="inlineStr" r="G95">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Robbinsville Jaguars</t>
         </is>
       </c>
       <c t="inlineStr" r="H95">
         <is>
-          <t xml:space="preserve">Monroe United</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I95">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="J95">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4493,7 @@
       </c>
       <c t="inlineStr" r="E96">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F96">
@@ -4513,22 +4503,22 @@
       </c>
       <c t="inlineStr" r="G96">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H96">
         <is>
-          <t xml:space="preserve">Invincible CC</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
       <c t="inlineStr" r="I96">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
       <c t="inlineStr" r="J96">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4538,7 @@
       </c>
       <c t="inlineStr" r="E97">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F97">
@@ -4558,22 +4548,22 @@
       </c>
       <c t="inlineStr" r="G97">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">Edison Riders</t>
         </is>
       </c>
       <c t="inlineStr" r="H97">
         <is>
-          <t xml:space="preserve">Kranti Warriors</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="I97">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
       <c t="inlineStr" r="J97">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4583,7 @@
       </c>
       <c t="inlineStr" r="E98">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F98">
@@ -4603,22 +4593,22 @@
       </c>
       <c t="inlineStr" r="G98">
         <is>
-          <t xml:space="preserve">Em Sports Club</t>
+          <t xml:space="preserve">Bethak Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="H98">
         <is>
-          <t xml:space="preserve">Telugu Titans - Weekenders</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I98">
         <is>
-          <t xml:space="preserve">EM Sports Club</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
       <c t="inlineStr" r="J98">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4628,7 @@
       </c>
       <c t="inlineStr" r="E99">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F99">
@@ -4648,22 +4638,22 @@
       </c>
       <c t="inlineStr" r="G99">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">Staten Island Strikers</t>
         </is>
       </c>
       <c t="inlineStr" r="H99">
         <is>
-          <t xml:space="preserve">JERSEY TIGERS</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I99">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J99">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4673,7 @@
       </c>
       <c t="inlineStr" r="E100">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F100">
@@ -4693,22 +4683,22 @@
       </c>
       <c t="inlineStr" r="G100">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">Phoenix Flyers</t>
         </is>
       </c>
       <c t="inlineStr" r="H100">
         <is>
-          <t xml:space="preserve">Mystery Squad</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I100">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">MCC - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J100">
         <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4718,7 @@
       </c>
       <c t="inlineStr" r="E101">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F101">
@@ -4738,22 +4728,22 @@
       </c>
       <c t="inlineStr" r="G101">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">Pmcc</t>
         </is>
       </c>
       <c t="inlineStr" r="H101">
         <is>
-          <t xml:space="preserve">Saffron Sapphire</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="I101">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="J101">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Em Sports Club</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4763,7 @@
       </c>
       <c t="inlineStr" r="E102">
         <is>
-          <t xml:space="preserve">09/19/2026</t>
+          <t xml:space="preserve">08/30/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F102">
@@ -4783,22 +4773,22 @@
       </c>
       <c t="inlineStr" r="G102">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">Perryville Panthers</t>
         </is>
       </c>
       <c t="inlineStr" r="H102">
         <is>
-          <t xml:space="preserve">Edison Kings</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I102">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J102">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4808,7 @@
       </c>
       <c t="inlineStr" r="E103">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F103">
@@ -4828,22 +4818,22 @@
       </c>
       <c t="inlineStr" r="G103">
         <is>
-          <t xml:space="preserve">Perryville Panthers</t>
+          <t xml:space="preserve">PRO SQUAD</t>
         </is>
       </c>
       <c t="inlineStr" r="H103">
         <is>
+          <t xml:space="preserve">JERSEY TIGERS</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I103">
+        <is>
+          <t xml:space="preserve">PRO SQUAD</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="J103">
+        <is>
           <t xml:space="preserve">MCC - Weekenders</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I103">
-        <is>
-          <t xml:space="preserve">MCC - Weekenders</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J103">
-        <is>
-          <t xml:space="preserve">Em Sports Club</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4853,7 @@
       </c>
       <c t="inlineStr" r="E104">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F104">
@@ -4873,22 +4863,22 @@
       </c>
       <c t="inlineStr" r="G104">
         <is>
-          <t xml:space="preserve">Pmcc</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H104">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">Mystery Squad</t>
         </is>
       </c>
       <c t="inlineStr" r="I104">
         <is>
-          <t xml:space="preserve">Sparta XI</t>
+          <t xml:space="preserve">MKCC Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J104">
         <is>
-          <t xml:space="preserve">JC Warriors</t>
+          <t xml:space="preserve">Plainsboro Panthers</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4898,7 @@
       </c>
       <c t="inlineStr" r="E105">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F105">
@@ -4918,22 +4908,22 @@
       </c>
       <c t="inlineStr" r="G105">
         <is>
-          <t xml:space="preserve">Phoenix Flyers</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="H105">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">Telugu Titans - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="I105">
         <is>
-          <t xml:space="preserve">Bayonne CC</t>
+          <t xml:space="preserve">Troy Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="J105">
         <is>
-          <t xml:space="preserve">Monroe Mavericks</t>
+          <t xml:space="preserve">Sparta XI</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4943,7 @@
       </c>
       <c t="inlineStr" r="E106">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F106">
@@ -4963,22 +4953,22 @@
       </c>
       <c t="inlineStr" r="G106">
         <is>
-          <t xml:space="preserve">Staten Island Strikers</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H106">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Kranti Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I106">
         <is>
-          <t xml:space="preserve">Jersey Sloggers</t>
+          <t xml:space="preserve">Sreeshti Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J106">
         <is>
-          <t xml:space="preserve">Express Rangers</t>
+          <t xml:space="preserve">Bayonne CC</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4988,7 @@
       </c>
       <c t="inlineStr" r="E107">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F107">
@@ -5008,22 +4998,22 @@
       </c>
       <c t="inlineStr" r="G107">
         <is>
-          <t xml:space="preserve">Bethak Titans</t>
+          <t xml:space="preserve">Em Sports Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H107">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">Invincible CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I107">
         <is>
-          <t xml:space="preserve">Newport Narcos</t>
+          <t xml:space="preserve">EM Sports Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J107">
         <is>
-          <t xml:space="preserve">Princeton Walk</t>
+          <t xml:space="preserve">Jersey Sloggers</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5033,7 @@
       </c>
       <c t="inlineStr" r="E108">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F108">
@@ -5053,22 +5043,22 @@
       </c>
       <c t="inlineStr" r="G108">
         <is>
-          <t xml:space="preserve">Edison Riders</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="H108">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">Monroe United</t>
         </is>
       </c>
       <c t="inlineStr" r="I108">
         <is>
-          <t xml:space="preserve">Parsippany Super Kings</t>
+          <t xml:space="preserve">JC Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J108">
         <is>
-          <t xml:space="preserve">Plainsboro Hunters</t>
+          <t xml:space="preserve">Newport Narcos</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5078,7 @@
       </c>
       <c t="inlineStr" r="E109">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F109">
@@ -5098,22 +5088,22 @@
       </c>
       <c t="inlineStr" r="G109">
         <is>
-          <t xml:space="preserve">SB Vikings Challengers Cricket Club</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="H109">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">Iselin Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="I109">
         <is>
-          <t xml:space="preserve">PCA Jr.</t>
+          <t xml:space="preserve">Monroe Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="J109">
         <is>
-          <t xml:space="preserve">MKCC Weekenders</t>
+          <t xml:space="preserve">Parsippany Super Kings</t>
         </is>
       </c>
     </row>
@@ -5133,32 +5123,32 @@
       </c>
       <c t="inlineStr" r="E110">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F110">
         <is>
-          <t xml:space="preserve">8:00 AM</t>
+          <t xml:space="preserve">08:00 AM</t>
         </is>
       </c>
       <c t="inlineStr" r="G110">
         <is>
-          <t xml:space="preserve">Robbinsville Jaguars</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
       <c t="inlineStr" r="H110">
         <is>
-          <t xml:space="preserve">TRIDENTS XI</t>
+          <t xml:space="preserve">NJKnights</t>
         </is>
       </c>
       <c t="inlineStr" r="I110">
         <is>
-          <t xml:space="preserve">TBD</t>
+          <t xml:space="preserve">Express Rangers</t>
         </is>
       </c>
       <c t="inlineStr" r="J110">
         <is>
-          <t xml:space="preserve">PRO SQUAD</t>
+          <t xml:space="preserve">PCA Jr.</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5168,7 @@
       </c>
       <c t="inlineStr" r="E111">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F111">
@@ -5188,22 +5178,22 @@
       </c>
       <c t="inlineStr" r="G111">
         <is>
-          <t xml:space="preserve">Mag11</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
       <c t="inlineStr" r="H111">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Saffron Sapphire</t>
         </is>
       </c>
       <c t="inlineStr" r="I111">
         <is>
-          <t xml:space="preserve">Cricket Warriors</t>
+          <t xml:space="preserve">Princeton Walk</t>
         </is>
       </c>
       <c t="inlineStr" r="J111">
         <is>
-          <t xml:space="preserve">Troy Titans</t>
+          <t xml:space="preserve">TRIDENTS XI</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5213,7 @@
       </c>
       <c t="inlineStr" r="E112">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F112">
@@ -5233,22 +5223,22 @@
       </c>
       <c t="inlineStr" r="G112">
         <is>
-          <t xml:space="preserve">Secaucus Fighters</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
       <c t="inlineStr" r="H112">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">Edison Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="I112">
         <is>
-          <t xml:space="preserve">Plainsboro Panthers</t>
+          <t xml:space="preserve">Plainsboro Hunters</t>
         </is>
       </c>
       <c t="inlineStr" r="J112">
         <is>
-          <t xml:space="preserve">Sreeshti Weekenders</t>
+          <t xml:space="preserve">Cricket Warriors</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5258,7 @@
       </c>
       <c t="inlineStr" r="E113">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F113">
@@ -5278,22 +5268,22 @@
       </c>
       <c t="inlineStr" r="G113">
         <is>
-          <t xml:space="preserve">Top Guns</t>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H113">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">Shreeji XI</t>
         </is>
       </c>
       <c t="inlineStr" r="I113">
         <is>
-          <t xml:space="preserve">Lincoln XI</t>
+          <t xml:space="preserve">SB Vikings Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J113">
         <is>
-          <t xml:space="preserve">GoldFinch Cricket Club</t>
+          <t xml:space="preserve">Windsor Warriors</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5303,7 @@
       </c>
       <c t="inlineStr" r="E114">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F114">
@@ -5323,22 +5313,22 @@
       </c>
       <c t="inlineStr" r="G114">
         <is>
-          <t xml:space="preserve">Monroe Giants Club</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
       <c t="inlineStr" r="H114">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">CHAMPIONS</t>
         </is>
       </c>
       <c t="inlineStr" r="I114">
         <is>
-          <t xml:space="preserve">Raptors</t>
+          <t xml:space="preserve">NJ Boxers</t>
         </is>
       </c>
       <c t="inlineStr" r="J114">
         <is>
-          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
+          <t xml:space="preserve">Lincoln XI</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5348,7 @@
       </c>
       <c t="inlineStr" r="E115">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F115">
@@ -5368,22 +5358,17 @@
       </c>
       <c t="inlineStr" r="G115">
         <is>
-          <t xml:space="preserve">Sinclair Lions</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
       <c t="inlineStr" r="H115">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
+          <t xml:space="preserve">Jc Mavericks</t>
         </is>
       </c>
       <c t="inlineStr" r="I115">
         <is>
-          <t xml:space="preserve">Brown Munde</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="J115">
-        <is>
-          <t xml:space="preserve">Karma XI</t>
+          <t xml:space="preserve">VRK Gladiators</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5388,7 @@
       </c>
       <c t="inlineStr" r="E116">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F116">
@@ -5413,22 +5398,22 @@
       </c>
       <c t="inlineStr" r="G116">
         <is>
-          <t xml:space="preserve">Jersey Aces</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="H116">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Morris Indians</t>
         </is>
       </c>
       <c t="inlineStr" r="I116">
         <is>
-          <t xml:space="preserve">Trident CC</t>
+          <t xml:space="preserve">Edison Warriors</t>
         </is>
       </c>
       <c t="inlineStr" r="J116">
         <is>
-          <t xml:space="preserve">Cricket Lovers</t>
+          <t xml:space="preserve">Brown Munde</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5433,7 @@
       </c>
       <c t="inlineStr" r="E117">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F117">
@@ -5458,22 +5443,22 @@
       </c>
       <c t="inlineStr" r="G117">
         <is>
-          <t xml:space="preserve">EB Strikers</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="H117">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">Jersey City Dominators</t>
         </is>
       </c>
       <c t="inlineStr" r="I117">
         <is>
-          <t xml:space="preserve">Waterfront Warriors</t>
+          <t xml:space="preserve">GoldFinch Cricket Club</t>
         </is>
       </c>
       <c t="inlineStr" r="J117">
         <is>
-          <t xml:space="preserve">Edison Super Kings</t>
+          <t xml:space="preserve">Trident CC</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5478,7 @@
       </c>
       <c t="inlineStr" r="E118">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F118">
@@ -5503,22 +5488,22 @@
       </c>
       <c t="inlineStr" r="G118">
         <is>
-          <t xml:space="preserve">Firehawks</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
       <c t="inlineStr" r="H118">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">NJ Titans</t>
         </is>
       </c>
       <c t="inlineStr" r="I118">
         <is>
-          <t xml:space="preserve">Thunder Strikers Weekenders</t>
+          <t xml:space="preserve">Hudson Hurricanes Sultans</t>
         </is>
       </c>
       <c t="inlineStr" r="J118">
         <is>
-          <t xml:space="preserve">RCW - Weekenders</t>
+          <t xml:space="preserve">Waterfront Warriors</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5523,7 @@
       </c>
       <c t="inlineStr" r="E119">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F119">
@@ -5548,22 +5533,22 @@
       </c>
       <c t="inlineStr" r="G119">
         <is>
-          <t xml:space="preserve">NJ Marvels</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
       <c t="inlineStr" r="H119">
         <is>
-          <t xml:space="preserve">Nj Warriors</t>
+          <t xml:space="preserve">BLOODLINE</t>
         </is>
       </c>
       <c t="inlineStr" r="I119">
         <is>
-          <t xml:space="preserve">NJ Warriors</t>
+          <t xml:space="preserve">Karma XI</t>
         </is>
       </c>
       <c t="inlineStr" r="J119">
         <is>
-          <t xml:space="preserve">SB Vikings Cricket Club</t>
+          <t xml:space="preserve">Thunder Strikers Weekenders</t>
         </is>
       </c>
     </row>
@@ -5583,7 +5568,7 @@
       </c>
       <c t="inlineStr" r="E120">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F120">
@@ -5593,22 +5578,22 @@
       </c>
       <c t="inlineStr" r="G120">
         <is>
-          <t xml:space="preserve">Giant Slayers</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
       <c t="inlineStr" r="H120">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Vikings CC</t>
         </is>
       </c>
       <c t="inlineStr" r="I120">
         <is>
-          <t xml:space="preserve">Incredibulls</t>
+          <t xml:space="preserve">Cricket Lovers</t>
         </is>
       </c>
       <c t="inlineStr" r="J120">
         <is>
-          <t xml:space="preserve">NJ Boxers</t>
+          <t xml:space="preserve">Nj Warriors</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5613,7 @@
       </c>
       <c t="inlineStr" r="E121">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F121">
@@ -5638,22 +5623,22 @@
       </c>
       <c t="inlineStr" r="G121">
         <is>
-          <t xml:space="preserve">Pway Cubs</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="H121">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Power Hitters</t>
         </is>
       </c>
       <c t="inlineStr" r="I121">
         <is>
-          <t xml:space="preserve">Jersey Superstars</t>
+          <t xml:space="preserve">Edison Super Kings</t>
         </is>
       </c>
       <c t="inlineStr" r="J121">
         <is>
-          <t xml:space="preserve">VRK Gladiators</t>
+          <t xml:space="preserve">Incredibulls</t>
         </is>
       </c>
     </row>
@@ -5673,7 +5658,7 @@
       </c>
       <c t="inlineStr" r="E122">
         <is>
-          <t xml:space="preserve">09/20/2026</t>
+          <t xml:space="preserve">08/29/2026</t>
         </is>
       </c>
       <c t="inlineStr" r="F122">
@@ -5683,22 +5668,22 @@
       </c>
       <c t="inlineStr" r="G122">
         <is>
-          <t xml:space="preserve">United Falcons</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="H122">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">Woodlot Boyz</t>
         </is>
       </c>
       <c t="inlineStr" r="I122">
         <is>
-          <t xml:space="preserve">Windsor Warriors</t>
+          <t xml:space="preserve">RCW - Weekenders</t>
         </is>
       </c>
       <c t="inlineStr" r="J122">
         <is>
-          <t xml:space="preserve">Edison Warriors</t>
+          <t xml:space="preserve">Jersey Superstars</t>
         </is>
       </c>
     </row>
